--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,127 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127505226</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137327251</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478832</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6970743</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Morgan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Morgan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137327251</t>
         </is>
       </c>
     </row>
@@ -902,6 +1023,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2472-2023 artfynd.xlsx
+++ b/artfynd/S 2472-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>137327251</v>
       </c>
       <c r="B4" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
